--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenCost_v2.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenCost_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>灵魂宝石（套装）（初始）</t>
+  </si>
+  <si>
+    <t>失败退到5级</t>
   </si>
   <si>
     <t>灵魂宝石（镶宝）</t>
@@ -883,6 +886,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -890,6 +896,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -897,17 +906,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1510,10 +1513,10 @@
       <c r="H2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1582,1126 +1585,1126 @@
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:10">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="11">
         <v>10000</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>10000</v>
       </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11">
-        <v>0</v>
-      </c>
-      <c r="I5" s="18" t="s">
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:10">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
         <v>1</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="11">
         <v>6000</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>6000</v>
       </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0</v>
-      </c>
-      <c r="I6" s="18" t="s">
+      <c r="G6" s="11">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:10">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
         <v>1</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="11">
         <v>6000</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>6000</v>
       </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18" t="s">
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:10">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="10">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="11">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="11">
         <v>5000</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>5000</v>
       </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18" t="s">
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:10">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="C9" s="11">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11">
         <v>1</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="11">
         <v>5000</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>5000</v>
       </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18" t="s">
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:10">
-      <c r="A10" s="9">
+      <c r="A10" s="10">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="10">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11">
         <v>1</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="11">
         <v>5000</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>5000</v>
       </c>
-      <c r="G10" s="10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18" t="s">
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:10">
-      <c r="A11" s="9">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="10">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10">
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="11">
         <v>5000</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>5000</v>
       </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18" t="s">
+      <c r="G11" s="11">
+        <v>5</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:10">
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="11">
+        <v>4000</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J12" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:10">
-      <c r="A12" s="9">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10" t="s">
+    <row r="13" s="2" customFormat="1" spans="1:10">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11">
+        <v>4000</v>
+      </c>
+      <c r="F13" s="11">
+        <v>4000</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:10">
+      <c r="A14" s="14">
+        <v>10</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>10000</v>
+      </c>
+      <c r="F14" s="15">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:10">
+      <c r="A15" s="14">
+        <v>11</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F15" s="15">
+        <v>6000</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:10">
+      <c r="A16" s="14">
+        <v>12</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="15">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F16" s="15">
+        <v>6000</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:10">
+      <c r="A17" s="14">
+        <v>13</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="15">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>5000</v>
+      </c>
+      <c r="F17" s="15">
+        <v>5000</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:10">
+      <c r="A18" s="14">
+        <v>14</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="15">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>5000</v>
+      </c>
+      <c r="F18" s="15">
+        <v>5000</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:10">
+      <c r="A19" s="14">
+        <v>15</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>5000</v>
+      </c>
+      <c r="F19" s="15">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <v>0</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:10">
+      <c r="A20" s="14">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="F20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="15">
+        <v>5</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10">
+      <c r="J20" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:10">
+      <c r="A21" s="14">
+        <v>17</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="15">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15">
         <v>1</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E21" s="15">
         <v>4000</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F21" s="15">
         <v>4000</v>
       </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18" t="s">
+      <c r="G21" s="15">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:10">
-      <c r="A13" s="9">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10">
+      <c r="J21" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:10">
+      <c r="A22" s="14">
+        <v>18</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E22" s="15">
         <v>4000</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F22" s="15">
         <v>4000</v>
       </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18" t="s">
+      <c r="G22" s="15">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="1:10">
-      <c r="A14" s="12">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <v>1</v>
-      </c>
-      <c r="E14" s="13">
-        <v>10000</v>
-      </c>
-      <c r="F14" s="13">
-        <v>10000</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>0</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:10">
-      <c r="A15" s="12">
-        <v>11</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13">
-        <v>6000</v>
-      </c>
-      <c r="F15" s="13">
-        <v>6000</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:10">
-      <c r="A16" s="12">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="J22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="13">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13">
-        <v>6000</v>
-      </c>
-      <c r="F16" s="13">
-        <v>6000</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:10">
-      <c r="A17" s="12">
-        <v>13</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13">
-        <v>5000</v>
-      </c>
-      <c r="F17" s="13">
-        <v>5000</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>0</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:10">
-      <c r="A18" s="12">
-        <v>14</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13">
-        <v>5000</v>
-      </c>
-      <c r="F18" s="13">
-        <v>5000</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>0</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:10">
-      <c r="A19" s="12">
-        <v>15</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <v>1</v>
-      </c>
-      <c r="E19" s="13">
-        <v>5000</v>
-      </c>
-      <c r="F19" s="13">
-        <v>5000</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>0</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:10">
-      <c r="A20" s="12">
-        <v>16</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <v>1</v>
-      </c>
-      <c r="E20" s="13">
-        <v>5000</v>
-      </c>
-      <c r="F20" s="13">
-        <v>5000</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>0</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:10">
-      <c r="A21" s="12">
-        <v>17</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13">
-        <v>4000</v>
-      </c>
-      <c r="F21" s="13">
-        <v>4000</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14">
-        <v>0</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:10">
-      <c r="A22" s="12">
-        <v>18</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13">
-        <v>4000</v>
-      </c>
-      <c r="F22" s="13">
-        <v>4000</v>
-      </c>
-      <c r="G22" s="13">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
+    </row>
+    <row r="23" spans="1:10">
       <c r="B23" s="5"/>
-      <c r="C23" s="15"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="C23" s="18"/>
+      <c r="H23" s="19"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="B24" s="5"/>
-      <c r="C24" s="15"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="C24" s="18"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="B25" s="5"/>
-      <c r="C25" s="15"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="C25" s="18"/>
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="B26" s="5"/>
-      <c r="C26" s="15"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="2:8">
+      <c r="C26" s="18"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="B27" s="5"/>
-      <c r="C27" s="15"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="28" spans="2:8">
+      <c r="C27" s="18"/>
+      <c r="H27" s="19"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="B28" s="5"/>
-      <c r="C28" s="15"/>
-      <c r="H28" s="16"/>
-    </row>
-    <row r="29" spans="2:8">
+      <c r="C28" s="18"/>
+      <c r="H28" s="19"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="B29" s="5"/>
-      <c r="C29" s="15"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" spans="2:8">
+      <c r="C29" s="18"/>
+      <c r="H29" s="19"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="B30" s="5"/>
-      <c r="C30" s="15"/>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="C30" s="18"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="B31" s="5"/>
-      <c r="C31" s="15"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="8:8">
-      <c r="H32" s="16"/>
+      <c r="C31" s="18"/>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="8:8">
-      <c r="H33" s="16"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="16"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="16"/>
+      <c r="H35" s="19"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="16"/>
+      <c r="H36" s="19"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="16"/>
+      <c r="H37" s="19"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="16"/>
+      <c r="H38" s="19"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="16"/>
+      <c r="H39" s="19"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="16"/>
+      <c r="H40" s="19"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="16"/>
+      <c r="H41" s="19"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="16"/>
+      <c r="H42" s="19"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="16"/>
+      <c r="H43" s="19"/>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="16"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="45" spans="8:8">
-      <c r="H45" s="16"/>
+      <c r="H45" s="19"/>
     </row>
     <row r="46" spans="8:8">
-      <c r="H46" s="16"/>
+      <c r="H46" s="19"/>
     </row>
     <row r="47" spans="8:8">
-      <c r="H47" s="16"/>
+      <c r="H47" s="19"/>
     </row>
     <row r="48" spans="8:8">
-      <c r="H48" s="16"/>
+      <c r="H48" s="19"/>
     </row>
     <row r="49" spans="8:8">
-      <c r="H49" s="16"/>
+      <c r="H49" s="19"/>
     </row>
     <row r="50" spans="8:8">
-      <c r="H50" s="16"/>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="8:8">
-      <c r="H51" s="16"/>
+      <c r="H51" s="19"/>
     </row>
     <row r="52" spans="8:8">
-      <c r="H52" s="16"/>
+      <c r="H52" s="19"/>
     </row>
     <row r="53" spans="8:8">
-      <c r="H53" s="16"/>
+      <c r="H53" s="19"/>
     </row>
     <row r="54" spans="8:8">
-      <c r="H54" s="16"/>
+      <c r="H54" s="19"/>
     </row>
     <row r="55" spans="8:8">
-      <c r="H55" s="16"/>
+      <c r="H55" s="19"/>
     </row>
     <row r="56" spans="8:8">
-      <c r="H56" s="16"/>
+      <c r="H56" s="19"/>
     </row>
     <row r="57" spans="8:8">
-      <c r="H57" s="16"/>
+      <c r="H57" s="19"/>
     </row>
     <row r="58" spans="8:8">
-      <c r="H58" s="16"/>
+      <c r="H58" s="19"/>
     </row>
     <row r="59" spans="8:8">
-      <c r="H59" s="16"/>
+      <c r="H59" s="19"/>
     </row>
     <row r="60" spans="8:8">
-      <c r="H60" s="16"/>
+      <c r="H60" s="19"/>
     </row>
     <row r="61" spans="8:8">
-      <c r="H61" s="16"/>
+      <c r="H61" s="19"/>
     </row>
     <row r="62" spans="8:8">
-      <c r="H62" s="16"/>
+      <c r="H62" s="19"/>
     </row>
     <row r="63" spans="8:8">
-      <c r="H63" s="16"/>
+      <c r="H63" s="19"/>
     </row>
     <row r="64" spans="8:8">
-      <c r="H64" s="16"/>
+      <c r="H64" s="19"/>
     </row>
     <row r="65" spans="8:8">
-      <c r="H65" s="16"/>
+      <c r="H65" s="19"/>
     </row>
     <row r="66" spans="8:8">
-      <c r="H66" s="16"/>
+      <c r="H66" s="19"/>
     </row>
     <row r="67" spans="8:8">
-      <c r="H67" s="16"/>
+      <c r="H67" s="19"/>
     </row>
     <row r="68" spans="8:8">
-      <c r="H68" s="16"/>
+      <c r="H68" s="19"/>
     </row>
     <row r="69" spans="8:8">
-      <c r="H69" s="16"/>
+      <c r="H69" s="19"/>
     </row>
     <row r="70" spans="8:8">
-      <c r="H70" s="16"/>
+      <c r="H70" s="19"/>
     </row>
     <row r="71" spans="8:8">
-      <c r="H71" s="16"/>
+      <c r="H71" s="19"/>
     </row>
     <row r="72" spans="8:8">
-      <c r="H72" s="16"/>
+      <c r="H72" s="19"/>
     </row>
     <row r="73" spans="8:8">
-      <c r="H73" s="16"/>
+      <c r="H73" s="19"/>
     </row>
     <row r="74" spans="8:8">
-      <c r="H74" s="16"/>
+      <c r="H74" s="19"/>
     </row>
     <row r="75" spans="8:8">
-      <c r="H75" s="16"/>
+      <c r="H75" s="19"/>
     </row>
     <row r="76" spans="8:8">
-      <c r="H76" s="16"/>
+      <c r="H76" s="19"/>
     </row>
     <row r="77" spans="8:8">
-      <c r="H77" s="16"/>
+      <c r="H77" s="19"/>
     </row>
     <row r="78" spans="8:8">
-      <c r="H78" s="16"/>
+      <c r="H78" s="19"/>
     </row>
     <row r="79" spans="8:8">
-      <c r="H79" s="16"/>
+      <c r="H79" s="19"/>
     </row>
     <row r="80" spans="8:8">
-      <c r="H80" s="16"/>
+      <c r="H80" s="19"/>
     </row>
     <row r="81" spans="8:8">
-      <c r="H81" s="16"/>
+      <c r="H81" s="19"/>
     </row>
     <row r="82" spans="8:8">
-      <c r="H82" s="16"/>
+      <c r="H82" s="19"/>
     </row>
     <row r="83" spans="8:8">
-      <c r="H83" s="16"/>
+      <c r="H83" s="19"/>
     </row>
     <row r="84" spans="8:8">
-      <c r="H84" s="16"/>
+      <c r="H84" s="19"/>
     </row>
     <row r="85" spans="8:8">
-      <c r="H85" s="16"/>
+      <c r="H85" s="19"/>
     </row>
     <row r="86" spans="8:8">
-      <c r="H86" s="16"/>
+      <c r="H86" s="19"/>
     </row>
     <row r="87" spans="8:8">
-      <c r="H87" s="16"/>
+      <c r="H87" s="19"/>
     </row>
     <row r="88" spans="8:8">
-      <c r="H88" s="16"/>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="8:8">
-      <c r="H89" s="16"/>
+      <c r="H89" s="19"/>
     </row>
     <row r="90" spans="8:8">
-      <c r="H90" s="16"/>
+      <c r="H90" s="19"/>
     </row>
     <row r="91" spans="8:8">
-      <c r="H91" s="16"/>
+      <c r="H91" s="19"/>
     </row>
     <row r="92" spans="8:8">
-      <c r="H92" s="16"/>
+      <c r="H92" s="19"/>
     </row>
     <row r="93" spans="8:8">
-      <c r="H93" s="16"/>
+      <c r="H93" s="19"/>
     </row>
     <row r="94" spans="8:8">
-      <c r="H94" s="16"/>
+      <c r="H94" s="19"/>
     </row>
     <row r="95" spans="8:8">
-      <c r="H95" s="16"/>
+      <c r="H95" s="19"/>
     </row>
     <row r="96" spans="8:8">
-      <c r="H96" s="16"/>
+      <c r="H96" s="19"/>
     </row>
     <row r="97" spans="8:8">
-      <c r="H97" s="16"/>
+      <c r="H97" s="19"/>
     </row>
     <row r="98" spans="8:8">
-      <c r="H98" s="16"/>
+      <c r="H98" s="19"/>
     </row>
     <row r="99" spans="8:8">
-      <c r="H99" s="16"/>
+      <c r="H99" s="19"/>
     </row>
     <row r="100" spans="8:8">
-      <c r="H100" s="16"/>
+      <c r="H100" s="19"/>
     </row>
     <row r="101" spans="8:8">
-      <c r="H101" s="16"/>
+      <c r="H101" s="19"/>
     </row>
     <row r="102" spans="8:8">
-      <c r="H102" s="16"/>
+      <c r="H102" s="19"/>
     </row>
     <row r="103" spans="8:8">
-      <c r="H103" s="16"/>
+      <c r="H103" s="19"/>
     </row>
     <row r="104" spans="8:8">
-      <c r="H104" s="16"/>
+      <c r="H104" s="19"/>
     </row>
     <row r="105" spans="8:8">
-      <c r="H105" s="16"/>
+      <c r="H105" s="19"/>
     </row>
     <row r="106" spans="8:8">
-      <c r="H106" s="16"/>
+      <c r="H106" s="19"/>
     </row>
     <row r="107" spans="8:8">
-      <c r="H107" s="16"/>
+      <c r="H107" s="19"/>
     </row>
     <row r="108" spans="8:8">
-      <c r="H108" s="16"/>
+      <c r="H108" s="19"/>
     </row>
     <row r="109" spans="8:8">
-      <c r="H109" s="16"/>
+      <c r="H109" s="19"/>
     </row>
     <row r="110" spans="8:8">
-      <c r="H110" s="16"/>
+      <c r="H110" s="19"/>
     </row>
     <row r="111" spans="8:8">
-      <c r="H111" s="16"/>
+      <c r="H111" s="19"/>
     </row>
     <row r="112" spans="8:8">
-      <c r="H112" s="16"/>
+      <c r="H112" s="19"/>
     </row>
     <row r="113" spans="8:8">
-      <c r="H113" s="16"/>
+      <c r="H113" s="19"/>
     </row>
     <row r="114" spans="8:8">
-      <c r="H114" s="16"/>
+      <c r="H114" s="19"/>
     </row>
     <row r="115" spans="8:8">
-      <c r="H115" s="16"/>
+      <c r="H115" s="19"/>
     </row>
     <row r="116" spans="8:8">
-      <c r="H116" s="16"/>
+      <c r="H116" s="19"/>
     </row>
     <row r="117" spans="8:8">
-      <c r="H117" s="16"/>
+      <c r="H117" s="19"/>
     </row>
     <row r="118" spans="8:8">
-      <c r="H118" s="16"/>
+      <c r="H118" s="19"/>
     </row>
     <row r="119" spans="8:8">
-      <c r="H119" s="16"/>
+      <c r="H119" s="19"/>
     </row>
     <row r="120" spans="8:8">
-      <c r="H120" s="16"/>
+      <c r="H120" s="19"/>
     </row>
     <row r="121" spans="8:8">
-      <c r="H121" s="16"/>
+      <c r="H121" s="19"/>
     </row>
     <row r="122" spans="8:8">
-      <c r="H122" s="16"/>
+      <c r="H122" s="19"/>
     </row>
     <row r="123" spans="8:8">
-      <c r="H123" s="16"/>
+      <c r="H123" s="19"/>
     </row>
     <row r="124" spans="8:8">
-      <c r="H124" s="16"/>
+      <c r="H124" s="19"/>
     </row>
     <row r="125" spans="8:8">
-      <c r="H125" s="16"/>
+      <c r="H125" s="19"/>
     </row>
     <row r="126" spans="8:8">
-      <c r="H126" s="16"/>
+      <c r="H126" s="19"/>
     </row>
     <row r="127" spans="8:8">
-      <c r="H127" s="16"/>
+      <c r="H127" s="19"/>
     </row>
     <row r="128" spans="8:8">
-      <c r="H128" s="16"/>
+      <c r="H128" s="19"/>
     </row>
     <row r="129" spans="8:8">
-      <c r="H129" s="16"/>
+      <c r="H129" s="19"/>
     </row>
     <row r="130" spans="8:8">
-      <c r="H130" s="16"/>
+      <c r="H130" s="19"/>
     </row>
     <row r="131" spans="8:8">
-      <c r="H131" s="16"/>
+      <c r="H131" s="19"/>
     </row>
     <row r="132" spans="8:8">
-      <c r="H132" s="16"/>
+      <c r="H132" s="19"/>
     </row>
     <row r="133" spans="8:8">
-      <c r="H133" s="16"/>
+      <c r="H133" s="19"/>
     </row>
     <row r="134" spans="8:8">
-      <c r="H134" s="16"/>
+      <c r="H134" s="19"/>
     </row>
     <row r="135" spans="8:8">
-      <c r="H135" s="16"/>
+      <c r="H135" s="19"/>
     </row>
     <row r="136" spans="8:8">
-      <c r="H136" s="16"/>
+      <c r="H136" s="19"/>
     </row>
     <row r="137" spans="8:8">
-      <c r="H137" s="16"/>
+      <c r="H137" s="19"/>
     </row>
     <row r="138" spans="8:8">
-      <c r="H138" s="16"/>
+      <c r="H138" s="19"/>
     </row>
     <row r="139" spans="8:8">
-      <c r="H139" s="16"/>
+      <c r="H139" s="19"/>
     </row>
     <row r="140" spans="8:8">
-      <c r="H140" s="16"/>
+      <c r="H140" s="19"/>
     </row>
     <row r="141" spans="8:8">
-      <c r="H141" s="16"/>
+      <c r="H141" s="19"/>
     </row>
     <row r="142" spans="8:8">
-      <c r="H142" s="16"/>
+      <c r="H142" s="19"/>
     </row>
     <row r="143" spans="8:8">
-      <c r="H143" s="16"/>
+      <c r="H143" s="19"/>
     </row>
     <row r="144" spans="8:8">
-      <c r="H144" s="16"/>
+      <c r="H144" s="19"/>
     </row>
     <row r="145" spans="8:8">
-      <c r="H145" s="16"/>
+      <c r="H145" s="19"/>
     </row>
     <row r="146" spans="8:8">
-      <c r="H146" s="16"/>
+      <c r="H146" s="19"/>
     </row>
     <row r="147" spans="8:8">
-      <c r="H147" s="16"/>
+      <c r="H147" s="19"/>
     </row>
     <row r="148" spans="8:8">
-      <c r="H148" s="16"/>
+      <c r="H148" s="19"/>
     </row>
     <row r="149" spans="8:8">
-      <c r="H149" s="16"/>
+      <c r="H149" s="19"/>
     </row>
     <row r="150" spans="8:8">
-      <c r="H150" s="16"/>
+      <c r="H150" s="19"/>
     </row>
     <row r="151" spans="8:8">
-      <c r="H151" s="16"/>
+      <c r="H151" s="19"/>
     </row>
     <row r="152" spans="8:8">
-      <c r="H152" s="16"/>
+      <c r="H152" s="19"/>
     </row>
     <row r="153" spans="8:8">
-      <c r="H153" s="16"/>
+      <c r="H153" s="19"/>
     </row>
     <row r="154" spans="8:8">
-      <c r="H154" s="16"/>
+      <c r="H154" s="19"/>
     </row>
     <row r="155" spans="8:8">
-      <c r="H155" s="16"/>
+      <c r="H155" s="19"/>
     </row>
     <row r="156" spans="8:8">
-      <c r="H156" s="16"/>
+      <c r="H156" s="19"/>
     </row>
     <row r="157" spans="8:8">
-      <c r="H157" s="16"/>
+      <c r="H157" s="19"/>
     </row>
     <row r="158" spans="8:8">
-      <c r="H158" s="16"/>
+      <c r="H158" s="19"/>
     </row>
     <row r="159" spans="8:8">
-      <c r="H159" s="16"/>
+      <c r="H159" s="19"/>
     </row>
     <row r="160" spans="8:8">
-      <c r="H160" s="16"/>
+      <c r="H160" s="19"/>
     </row>
     <row r="161" spans="8:8">
-      <c r="H161" s="16"/>
+      <c r="H161" s="19"/>
     </row>
     <row r="162" spans="8:8">
-      <c r="H162" s="16"/>
+      <c r="H162" s="19"/>
     </row>
     <row r="163" spans="8:8">
-      <c r="H163" s="16"/>
+      <c r="H163" s="19"/>
     </row>
     <row r="164" spans="8:8">
-      <c r="H164" s="16"/>
+      <c r="H164" s="19"/>
     </row>
     <row r="165" spans="8:8">
-      <c r="H165" s="16"/>
+      <c r="H165" s="19"/>
     </row>
     <row r="166" spans="8:8">
-      <c r="H166" s="16"/>
+      <c r="H166" s="19"/>
     </row>
     <row r="167" spans="8:8">
-      <c r="H167" s="16"/>
+      <c r="H167" s="19"/>
     </row>
     <row r="168" spans="8:8">
-      <c r="H168" s="16"/>
+      <c r="H168" s="19"/>
     </row>
     <row r="169" spans="8:8">
-      <c r="H169" s="16"/>
+      <c r="H169" s="19"/>
     </row>
     <row r="170" spans="8:8">
-      <c r="H170" s="16"/>
+      <c r="H170" s="19"/>
     </row>
     <row r="171" spans="8:8">
-      <c r="H171" s="16"/>
+      <c r="H171" s="19"/>
     </row>
     <row r="172" spans="8:8">
-      <c r="H172" s="16"/>
+      <c r="H172" s="19"/>
     </row>
     <row r="173" spans="8:8">
-      <c r="H173" s="16"/>
+      <c r="H173" s="19"/>
     </row>
     <row r="174" spans="8:8">
-      <c r="H174" s="16"/>
+      <c r="H174" s="19"/>
     </row>
     <row r="175" spans="8:8">
-      <c r="H175" s="16"/>
+      <c r="H175" s="19"/>
     </row>
     <row r="176" spans="8:8">
-      <c r="H176" s="16"/>
+      <c r="H176" s="19"/>
     </row>
     <row r="177" spans="8:8">
-      <c r="H177" s="16"/>
+      <c r="H177" s="19"/>
     </row>
     <row r="178" spans="8:8">
-      <c r="H178" s="16"/>
+      <c r="H178" s="19"/>
     </row>
     <row r="179" spans="8:8">
-      <c r="H179" s="16"/>
+      <c r="H179" s="19"/>
     </row>
     <row r="180" spans="8:8">
-      <c r="H180" s="16"/>
+      <c r="H180" s="19"/>
     </row>
     <row r="181" spans="8:8">
-      <c r="H181" s="16"/>
+      <c r="H181" s="19"/>
     </row>
     <row r="182" spans="8:8">
-      <c r="H182" s="16"/>
+      <c r="H182" s="19"/>
     </row>
     <row r="183" spans="8:8">
-      <c r="H183" s="16"/>
+      <c r="H183" s="19"/>
     </row>
     <row r="184" spans="8:8">
-      <c r="H184" s="16"/>
+      <c r="H184" s="19"/>
     </row>
     <row r="185" spans="8:8">
-      <c r="H185" s="16"/>
+      <c r="H185" s="19"/>
     </row>
     <row r="186" spans="8:8">
-      <c r="H186" s="16"/>
+      <c r="H186" s="19"/>
     </row>
     <row r="187" spans="8:8">
-      <c r="H187" s="16"/>
+      <c r="H187" s="19"/>
     </row>
     <row r="188" spans="8:8">
-      <c r="H188" s="16"/>
+      <c r="H188" s="19"/>
     </row>
     <row r="189" spans="8:8">
-      <c r="H189" s="16"/>
+      <c r="H189" s="19"/>
     </row>
     <row r="190" spans="8:8">
-      <c r="H190" s="16"/>
+      <c r="H190" s="19"/>
     </row>
     <row r="191" spans="8:8">
-      <c r="H191" s="16"/>
+      <c r="H191" s="19"/>
     </row>
     <row r="192" spans="8:8">
-      <c r="H192" s="16"/>
+      <c r="H192" s="19"/>
     </row>
     <row r="193" spans="8:8">
-      <c r="H193" s="16"/>
+      <c r="H193" s="19"/>
     </row>
     <row r="194" spans="8:8">
-      <c r="H194" s="16"/>
+      <c r="H194" s="19"/>
     </row>
     <row r="195" spans="8:8">
-      <c r="H195" s="16"/>
+      <c r="H195" s="19"/>
     </row>
     <row r="196" spans="8:8">
-      <c r="H196" s="16"/>
+      <c r="H196" s="19"/>
     </row>
     <row r="197" spans="8:8">
-      <c r="H197" s="16"/>
+      <c r="H197" s="19"/>
     </row>
     <row r="198" spans="8:8">
-      <c r="H198" s="16"/>
+      <c r="H198" s="19"/>
     </row>
     <row r="199" spans="8:8">
       <c r="H199" s="20"/>
